--- a/exports/002352.SZ_20260315.xlsx
+++ b/exports/002352.SZ_20260315.xlsx
@@ -436,7 +436,7 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -564,7 +564,7 @@
         <v>0.72</v>
       </c>
       <c r="I2" t="n">
-        <v>421500.51</v>
+        <v>421501</v>
       </c>
       <c r="J2" t="n">
         <v>1599400.019</v>
@@ -621,7 +621,7 @@
         <v>0.02</v>
       </c>
       <c r="I3" t="n">
-        <v>162838.64</v>
+        <v>162839</v>
       </c>
       <c r="J3" t="n">
         <v>606695.404</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>161546.06</v>
+        <v>161546</v>
       </c>
       <c r="J4" t="n">
         <v>603032.603</v>
@@ -735,7 +735,7 @@
         <v>0.41</v>
       </c>
       <c r="I5" t="n">
-        <v>171734.62</v>
+        <v>171735</v>
       </c>
       <c r="J5" t="n">
         <v>638643.274</v>
@@ -792,7 +792,7 @@
         <v>-0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>240574.21</v>
+        <v>240574</v>
       </c>
       <c r="J6" t="n">
         <v>885114.753</v>
@@ -849,7 +849,7 @@
         <v>0.53</v>
       </c>
       <c r="I7" t="n">
-        <v>234229.2</v>
+        <v>234229</v>
       </c>
       <c r="J7" t="n">
         <v>866732.5600000001</v>
@@ -906,7 +906,7 @@
         <v>0.43</v>
       </c>
       <c r="I8" t="n">
-        <v>209951.37</v>
+        <v>209951</v>
       </c>
       <c r="J8" t="n">
         <v>768867.175</v>
@@ -963,7 +963,7 @@
         <v>-0.74</v>
       </c>
       <c r="I9" t="n">
-        <v>372789.55</v>
+        <v>372790</v>
       </c>
       <c r="J9" t="n">
         <v>1353478.323</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>291284.48</v>
+        <v>291284</v>
       </c>
       <c r="J10" t="n">
         <v>1083265.944</v>
@@ -1077,7 +1077,7 @@
         <v>-0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>454111.71</v>
+        <v>454112</v>
       </c>
       <c r="J11" t="n">
         <v>1682048.622</v>
@@ -1134,7 +1134,7 @@
         <v>0.37</v>
       </c>
       <c r="I12" t="n">
-        <v>343557.76</v>
+        <v>343558</v>
       </c>
       <c r="J12" t="n">
         <v>1301985.638</v>
@@ -1191,7 +1191,7 @@
         <v>-0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>351900.81</v>
+        <v>351901</v>
       </c>
       <c r="J13" t="n">
         <v>1319077.719</v>
@@ -1248,7 +1248,7 @@
         <v>-0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>322464.44</v>
+        <v>322464</v>
       </c>
       <c r="J14" t="n">
         <v>1216186.057</v>
@@ -1305,7 +1305,7 @@
         <v>-0.19</v>
       </c>
       <c r="I15" t="n">
-        <v>253842.66</v>
+        <v>253843</v>
       </c>
       <c r="J15" t="n">
         <v>957130.534</v>
@@ -1362,7 +1362,7 @@
         <v>-0.34</v>
       </c>
       <c r="I16" t="n">
-        <v>190946.78</v>
+        <v>190947</v>
       </c>
       <c r="J16" t="n">
         <v>724598.518</v>
@@ -1419,7 +1419,7 @@
         <v>-0.38</v>
       </c>
       <c r="I17" t="n">
-        <v>219260.68</v>
+        <v>219261</v>
       </c>
       <c r="J17" t="n">
         <v>838835.848</v>
@@ -1476,7 +1476,7 @@
         <v>-0.26</v>
       </c>
       <c r="I18" t="n">
-        <v>202553.85</v>
+        <v>202554</v>
       </c>
       <c r="J18" t="n">
         <v>781443.147</v>
@@ -1533,7 +1533,7 @@
         <v>-0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>168994.15</v>
+        <v>168994</v>
       </c>
       <c r="J19" t="n">
         <v>657186.134</v>
@@ -1590,7 +1590,7 @@
         <v>0.11</v>
       </c>
       <c r="I20" t="n">
-        <v>228466.29</v>
+        <v>228466</v>
       </c>
       <c r="J20" t="n">
         <v>889312.387</v>
@@ -1645,7 +1645,7 @@
         <v>-0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>289763.39</v>
+        <v>289763</v>
       </c>
       <c r="J21" t="n">
         <v>1130215.566</v>
@@ -1700,7 +1700,7 @@
         <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>543935.58</v>
+        <v>543936</v>
       </c>
       <c r="J22" t="n">
         <v>2137757.102</v>
@@ -1755,7 +1755,7 @@
         <v>0.8</v>
       </c>
       <c r="I23" t="n">
-        <v>370312.86</v>
+        <v>370313</v>
       </c>
       <c r="J23" t="n">
         <v>1414447.754</v>
@@ -1810,7 +1810,7 @@
         <v>0.31</v>
       </c>
       <c r="I24" t="n">
-        <v>215981.08</v>
+        <v>215981</v>
       </c>
       <c r="J24" t="n">
         <v>809190.045</v>
@@ -1865,7 +1865,7 @@
         <v>-0.14</v>
       </c>
       <c r="I25" t="n">
-        <v>234408.31</v>
+        <v>234408</v>
       </c>
       <c r="J25" t="n">
         <v>877878.655</v>
@@ -1920,7 +1920,7 @@
         <v>-0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>294054.51</v>
+        <v>294055</v>
       </c>
       <c r="J26" t="n">
         <v>1108482.719</v>
@@ -1973,7 +1973,7 @@
         <v>0.44</v>
       </c>
       <c r="I27" t="n">
-        <v>367293.7</v>
+        <v>367294</v>
       </c>
       <c r="J27" t="n">
         <v>1388389.744</v>
@@ -2026,7 +2026,7 @@
         <v>-0.18</v>
       </c>
       <c r="I28" t="n">
-        <v>389818.17</v>
+        <v>389818</v>
       </c>
       <c r="J28" t="n">
         <v>1470523.508</v>
@@ -2079,7 +2079,7 @@
         <v>-0.89</v>
       </c>
       <c r="I29" t="n">
-        <v>398951.51</v>
+        <v>398952</v>
       </c>
       <c r="J29" t="n">
         <v>1521596.889</v>
@@ -2132,7 +2132,7 @@
         <v>-0.4</v>
       </c>
       <c r="I30" t="n">
-        <v>358803.03</v>
+        <v>358803</v>
       </c>
       <c r="J30" t="n">
         <v>1393024.109</v>
@@ -2183,7 +2183,7 @@
         <v>-0.52</v>
       </c>
       <c r="I31" t="n">
-        <v>406294.77</v>
+        <v>406295</v>
       </c>
       <c r="J31" t="n">
         <v>1595533.506</v>
@@ -2234,7 +2234,7 @@
         <v>0.17</v>
       </c>
       <c r="I32" t="n">
-        <v>304153.75</v>
+        <v>304154</v>
       </c>
       <c r="J32" t="n">
         <v>1210936.064</v>
@@ -2285,7 +2285,7 @@
         <v>-0.3</v>
       </c>
       <c r="I33" t="n">
-        <v>313928.78</v>
+        <v>313929</v>
       </c>
       <c r="J33" t="n">
         <v>1244459.098</v>
@@ -2336,7 +2336,7 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>615083.0600000001</v>
+        <v>615083</v>
       </c>
       <c r="J34" t="n">
         <v>2441237.443</v>
@@ -2387,7 +2387,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>307620.85</v>
+        <v>307621</v>
       </c>
       <c r="J35" t="n">
         <v>1188455.27</v>
@@ -2436,7 +2436,7 @@
         <v>-0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>309886.16</v>
+        <v>309886</v>
       </c>
       <c r="J36" t="n">
         <v>1204558.432</v>
@@ -2485,7 +2485,7 @@
         <v>0.64</v>
       </c>
       <c r="I37" t="n">
-        <v>474063.1</v>
+        <v>474063</v>
       </c>
       <c r="J37" t="n">
         <v>1870599.119</v>
@@ -2534,7 +2534,7 @@
         <v>-0.38</v>
       </c>
       <c r="I38" t="n">
-        <v>311413.48</v>
+        <v>311413</v>
       </c>
       <c r="J38" t="n">
         <v>1209057.74</v>
